--- a/docs/示例输出-预算表.xlsx
+++ b/docs/示例输出-预算表.xlsx
@@ -42,8 +42,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="7.2" customWidth="1"/>
-    <col min="2" max="2" width="26.4" customWidth="1"/>
-    <col min="3" max="3" width="31.2" customWidth="1"/>
+    <col min="2" max="2" width="24.0" customWidth="1"/>
+    <col min="3" max="3" width="33.6" customWidth="1"/>
     <col min="4" max="4" width="10.8" customWidth="1"/>
     <col min="5" max="5" width="16.8" customWidth="1"/>
   </cols>
@@ -101,7 +101,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">工日 80.50</t>
+          <t xml:space="preserve">技工 186.42 工日 + 普工 519.65 工日</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="E5">
-        <v>9177</v>
+        <v>52950.530000</v>
       </c>
     </row>
     <row r="6">
@@ -133,7 +133,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>11536.200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -156,7 +156,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>27.530000</v>
+        <v>158.850000</v>
       </c>
     </row>
     <row r="8">
@@ -179,7 +179,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -202,7 +202,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -225,7 +225,7 @@
         </is>
       </c>
       <c r="E10">
-        <v>21361.730000</v>
+        <v>53109.380000</v>
       </c>
     </row>
     <row r="11">
@@ -239,7 +239,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 9,177.00</t>
+          <t xml:space="preserve">人工费 52,950.53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -248,7 +248,7 @@
         </is>
       </c>
       <c r="E11">
-        <v>275.310000</v>
+        <v>1588.520000</v>
       </c>
     </row>
     <row r="12">
@@ -262,7 +262,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 9,177.00</t>
+          <t xml:space="preserve">人工费 52,950.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>137.660000</v>
+        <v>794.260000</v>
       </c>
     </row>
     <row r="13">
@@ -285,7 +285,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 9,177.00</t>
+          <t xml:space="preserve">人工费 52,950.53</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -294,7 +294,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>2294.250000</v>
+        <v>13237.630000</v>
       </c>
     </row>
     <row r="14">
@@ -308,7 +308,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 9,177.00</t>
+          <t xml:space="preserve">人工费 52,950.53</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -317,7 +317,7 @@
         </is>
       </c>
       <c r="E14">
-        <v>1101.240000</v>
+        <v>6354.060000</v>
       </c>
     </row>
     <row r="15">
@@ -331,7 +331,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 9,177.00</t>
+          <t xml:space="preserve">人工费 52,950.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -340,7 +340,7 @@
         </is>
       </c>
       <c r="E15">
-        <v>734.160000</v>
+        <v>4236.040000</v>
       </c>
     </row>
     <row r="16">
@@ -354,7 +354,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接费+措施费+间接费 25,904.35</t>
+          <t xml:space="preserve">直接费+措施费+间接费 79,319.89</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -363,7 +363,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>2331.390000</v>
+        <v>7138.790000</v>
       </c>
     </row>
     <row r="17">
@@ -377,7 +377,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">（一）～（8）</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -386,7 +386,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>412.970000</v>
+        <v>2382.770000</v>
       </c>
     </row>
     <row r="18">
@@ -409,7 +409,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>3395.490000</v>
+        <v>19591.700000</v>
       </c>
     </row>
     <row r="19">
@@ -432,7 +432,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>28235.740000</v>
+        <v>86458.680000</v>
       </c>
     </row>
     <row r="20">
@@ -460,18 +460,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="6.0" customWidth="1"/>
-    <col min="2" max="2" width="13.2" customWidth="1"/>
-    <col min="3" max="3" width="36.0" customWidth="1"/>
+    <col min="2" max="2" width="12.0" customWidth="1"/>
+    <col min="3" max="3" width="31.2" customWidth="1"/>
     <col min="4" max="4" width="8.4" customWidth="1"/>
-    <col min="5" max="5" width="10.8" customWidth="1"/>
-    <col min="6" max="6" width="9.6" customWidth="1"/>
-    <col min="7" max="7" width="10.8" customWidth="1"/>
-    <col min="8" max="8" width="13.2" customWidth="1"/>
-    <col min="9" max="9" width="13.2" customWidth="1"/>
+    <col min="5" max="5" width="9.6" customWidth="1"/>
+    <col min="6" max="6" width="8.4" customWidth="1"/>
+    <col min="7" max="7" width="10.2" customWidth="1"/>
+    <col min="8" max="8" width="10.2" customWidth="1"/>
+    <col min="9" max="9" width="12.0" customWidth="1"/>
     <col min="10" max="10" width="12.0" customWidth="1"/>
-    <col min="11" max="11" width="12.0" customWidth="1"/>
-    <col min="12" max="12" width="14.4" customWidth="1"/>
-    <col min="13" max="13" width="16.8" customWidth="1"/>
+    <col min="11" max="11" width="10.8" customWidth="1"/>
+    <col min="12" max="12" width="10.8" customWidth="1"/>
+    <col min="13" max="13" width="13.2" customWidth="1"/>
+    <col min="14" max="14" width="14.4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,40 +518,45 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">工日系数</t>
+          <t xml:space="preserve">系数</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">工日</t>
+          <t xml:space="preserve">技工工日</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t xml:space="preserve">普工工日</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t xml:space="preserve">人工费</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">主材费</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve">机械费</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">仪表费</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">小计</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">备注</t>
         </is>
@@ -567,12 +573,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">架空光缆敷设（挂钩法）</t>
+          <t xml:space="preserve">光（电）缆工程施工测量 直埋</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100m</t>
+          <t xml:space="preserve">百米</t>
         </is>
       </c>
       <c r="E5">
@@ -582,26 +588,29 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>30</v>
+        <v>6.720000</v>
       </c>
       <c r="H5">
-        <v>3420</v>
+        <v>1.680000</v>
       </c>
       <c r="I5">
-        <v>4536</v>
+        <v>868.560000</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>8038.260000</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">架空光缆 1200m</t>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>871.170000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施工测量 12 百米</t>
         </is>
       </c>
     </row>
@@ -611,17 +620,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TXL1-002</t>
+          <t xml:space="preserve">TXL2-001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">管道光缆敷设（人工牵引）</t>
+          <t xml:space="preserve">挖、松填光（电）缆沟及接头坑 普通土</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100m</t>
+          <t xml:space="preserve">百立方米</t>
         </is>
       </c>
       <c r="E6">
@@ -630,27 +639,32 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6">
-        <v>27.200000</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="H6">
-        <v>3100.800000</v>
+        <v>334.730000</v>
       </c>
       <c r="I6">
-        <v>4595.100000</v>
+        <v>20418.530000</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>7756.200000</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">管道光缆 850m</t>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>20479.790000</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">挖填缆沟</t>
         </is>
       </c>
     </row>
@@ -665,12 +679,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">光缆接续（24 芯以下）</t>
+          <t xml:space="preserve">光（电）缆工程施工测量 管道</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">头</t>
+          <t xml:space="preserve">百米</t>
         </is>
       </c>
       <c r="E7">
@@ -680,26 +694,29 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>10.800000</v>
+        <v>2.100000</v>
       </c>
       <c r="H7">
-        <v>1231.200000</v>
+        <v>0.540000</v>
       </c>
       <c r="I7">
-        <v>515.100000</v>
+        <v>272.340000</v>
       </c>
       <c r="J7">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2217.990000</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">接续 6 头</t>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>273.160000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">施工测量（管道）</t>
         </is>
       </c>
     </row>
@@ -714,12 +731,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">架空光缆敷设（挂钩法）</t>
+          <t xml:space="preserve">光（电）缆工程施工测量 直埋</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100m</t>
+          <t xml:space="preserve">百米</t>
         </is>
       </c>
       <c r="E8">
@@ -729,52 +746,105 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>12.500000</v>
+        <v>2.800000</v>
       </c>
       <c r="H8">
-        <v>1425</v>
+        <v>0.700000</v>
       </c>
       <c r="I8">
-        <v>1890</v>
+        <v>361.900000</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>3349.280000</v>
-      </c>
-      <c r="M8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>362.990000</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">重复行</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9">
+        <v>5</v>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t xml:space="preserve">TXL3-222</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">架空自承式电缆 100 对以上</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">千米条</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>174.800000</v>
+      </c>
+      <c r="H9">
+        <v>182</v>
+      </c>
+      <c r="I9">
+        <v>31029.200000</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>31122.290000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
           <t xml:space="preserve">合计</t>
         </is>
       </c>
-      <c r="F9">
-        <v>80.500000</v>
-      </c>
-      <c r="G9">
-        <v>9177</v>
-      </c>
-      <c r="H9">
-        <v>11536.200000</v>
-      </c>
-      <c r="I9">
-        <v>324</v>
-      </c>
-      <c r="J9">
-        <v>297</v>
-      </c>
-      <c r="K9">
-        <v>21361.730000</v>
+      <c r="G10">
+        <v>186.420000</v>
+      </c>
+      <c r="H10">
+        <v>519.650000</v>
+      </c>
+      <c r="I10">
+        <v>52950.530000</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>53109.380000</v>
       </c>
     </row>
   </sheetData>
@@ -862,27 +932,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">光缆</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GYTA-24B1.3</t>
+          <t xml:space="preserve">L 型挂钩</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">只</t>
         </is>
       </c>
       <c r="F5">
-        <v>2652</v>
+        <v>252.500000</v>
       </c>
       <c r="G5">
-        <v>3.200000</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8486.400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -896,27 +961,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">光缆接头盒</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24 芯</t>
+          <t xml:space="preserve">U 型卡子②</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">套</t>
+          <t xml:space="preserve">个</t>
         </is>
       </c>
       <c r="F6">
-        <v>6.060000</v>
+        <v>272.700000</v>
       </c>
       <c r="G6">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>515.100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -930,27 +990,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">塑料子管</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Φ28/32</t>
+          <t xml:space="preserve">三眼双曲槽夹板</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">副</t>
         </is>
       </c>
       <c r="F7">
-        <v>867</v>
+        <v>20.200000</v>
       </c>
       <c r="G7">
-        <v>2.100000</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1820.700000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -964,37 +1019,554 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">挂钩</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25mm</t>
+          <t xml:space="preserve">单眼曲槽夹板</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t xml:space="preserve">副</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>292.900000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吊线抱箍</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">套</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>282.800000</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">吊线担</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">根</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>282.800000</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圆帽穿钉 M12×60</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">副</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>252.500000</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圆帽穿钉 M12×80</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">副</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>252.500000</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多用二线钢担</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">根</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>282.800000</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">小拉板</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">块</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>30.300000</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拉线抱箍</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">套</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>40.400000</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拉线衬环</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t xml:space="preserve">个</t>
         </is>
       </c>
-      <c r="F8">
-        <v>2040</v>
-      </c>
-      <c r="G8">
-        <v>0.350000</v>
-      </c>
-      <c r="H8">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="F16">
+        <v>90.900000</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">终端可变抱箍</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">套</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>60.600000</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自承式电缆</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>10070</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">转弯夹板</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">副</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>20.200000</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">钢担 U 型抱箍（二线担用）</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">套</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>282.800000</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">钢线双向膨胀锁</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>20.200000</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">钢线终端膨胀锁</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>90.900000</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">镀锌穿钉 M12×80</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">副</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>10.100000</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">镀锌钢绞线 7/2.2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>25</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">镀锌铁线 ø1.5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>7.100000</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主材</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">镀锌铁线 ø2.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kg</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>10.200000</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t xml:space="preserve">合计</t>
         </is>
       </c>
-      <c r="H9">
-        <v>11536.200000</v>
+      <c r="H27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1082,12 +1654,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">光时域反射仪</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTDR</t>
+          <t xml:space="preserve">地下管线探测仪</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1096,13 +1663,13 @@
         </is>
       </c>
       <c r="F5">
-        <v>2.475000</v>
+        <v>0.850000</v>
       </c>
       <c r="G5">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1111,17 +1678,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">机械</t>
+          <t xml:space="preserve">仪表</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">光纤熔接机</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单芯</t>
+          <t xml:space="preserve">激光测距仪</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1130,13 +1692,13 @@
         </is>
       </c>
       <c r="F6">
-        <v>1.800000</v>
+        <v>0.920000</v>
       </c>
       <c r="G6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1146,7 +1708,7 @@
         </is>
       </c>
       <c r="H7">
-        <v>621</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/示例输出-预算表.xlsx
+++ b/docs/示例输出-预算表.xlsx
@@ -2,10 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="预算汇总表" sheetId="1" r:id="rId1"/>
-    <sheet name="定额明细表（表二）" sheetId="2" r:id="rId2"/>
-    <sheet name="主要材料（设备）表" sheetId="3" r:id="rId3"/>
-    <sheet name="机械仪表台班表" sheetId="4" r:id="rId4"/>
+    <sheet name="工程预算总表（表一）" sheetId="1" r:id="rId1"/>
+    <sheet name="建筑安装工程费用预算表（表二）" sheetId="2" r:id="rId2"/>
+    <sheet name="建筑安装工程量预算表（表三甲）" sheetId="3" r:id="rId3"/>
+    <sheet name="建筑安装工程机械使用费预算表（表三乙）" sheetId="4" r:id="rId4"/>
+    <sheet name="建筑安装工程仪器仪表使用费预算表（表三丙）" sheetId="5" r:id="rId5"/>
+    <sheet name="器材预算表（表四甲 · 国内器材）" sheetId="6" r:id="rId6"/>
+    <sheet name="工程建设其他费预算表（表五甲）" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -42,8 +45,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="7.2" customWidth="1"/>
-    <col min="2" max="2" width="24.0" customWidth="1"/>
-    <col min="3" max="3" width="33.6" customWidth="1"/>
+    <col min="2" max="2" width="26.4" customWidth="1"/>
+    <col min="3" max="3" width="31.2" customWidth="1"/>
     <col min="4" max="4" width="10.8" customWidth="1"/>
     <col min="5" max="5" width="16.8" customWidth="1"/>
   </cols>
@@ -51,14 +54,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">预算汇总表</t>
+          <t xml:space="preserve">工程预算总表（表一）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">工程编号：ZT-2026-001　工程名称：自检工程-架空光缆　专业：有线通信　建设单位：某运营商　施工单位：某工程公司</t>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
         </is>
       </c>
     </row>
@@ -91,17 +94,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费</t>
+          <t xml:space="preserve">建筑安装工程费</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">技工 186.42 工日 + 普工 519.65 工日</t>
+          <t xml:space="preserve">直接费+措施费+间接费+利润+税金</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -110,44 +115,34 @@
         </is>
       </c>
       <c r="E5">
-        <v>52950.530000</v>
+        <v>559541.800000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要材料费</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+          <t xml:space="preserve">直接费</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
       <c r="E6">
-        <v>0</v>
+        <v>403468.670000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">辅助材料费</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人工费 × 0.300%</t>
+          <t xml:space="preserve">措施费</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -156,67 +151,57 @@
         </is>
       </c>
       <c r="E7">
-        <v>158.850000</v>
+        <v>9810.040000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">机械使用费</t>
+          <t xml:space="preserve">间接费</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">规费+企业管理费</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
       <c r="E8">
-        <v>0</v>
+        <v>86328.340000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">仪表使用费</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+          <t xml:space="preserve">利润</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
       <c r="E9">
-        <v>0</v>
+        <v>13734.050000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接费小计</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">（一）～（五）</t>
+          <t xml:space="preserve">税金</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -225,230 +210,130 @@
         </is>
       </c>
       <c r="E10">
-        <v>53109.380000</v>
+        <v>46200.700000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>7</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">二</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">安全文明施工费</t>
+          <t xml:space="preserve">设备工器具购置费</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 52,950.53</t>
+          <t xml:space="preserve">单列，不计取费</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.000%</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E11">
-        <v>1588.520000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>8</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">临时设施费</t>
+          <t xml:space="preserve">工程建设其他费</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 52,950.53</t>
+          <t xml:space="preserve">见表五</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.500%</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E12">
-        <v>794.260000</v>
+        <v>36370.220000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>9</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">四</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">企业管理费</t>
+          <t xml:space="preserve">预备费</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 52,950.53</t>
+          <t xml:space="preserve">基本预备费</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.000%</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E13">
-        <v>13237.630000</v>
+        <v>17877.360000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>10</v>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">规费</t>
+          <t xml:space="preserve">工程总造价</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 52,950.53</t>
+          <t xml:space="preserve">一+二+三+四</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">12.000%</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E14">
-        <v>6354.060000</v>
+        <v>613789.380000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>11</v>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">利润</t>
+          <t xml:space="preserve">工程总造价（大写）</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">人工费 52,950.53</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8.000%</t>
-        </is>
-      </c>
-      <c r="E15">
-        <v>4236.040000</v>
+          <t xml:space="preserve">陆拾壹万叁仟柒佰捌拾玖元叁角捌分</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>12</v>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">税金（增值税）</t>
+          <t xml:space="preserve">编制人：示例</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接费+措施费+间接费 79,319.89</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9.000%</t>
-        </is>
-      </c>
-      <c r="E16">
-        <v>7138.790000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">措施费小计</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E17">
-        <v>2382.770000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">间接费小计</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E18">
-        <v>19591.700000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">建安工程费合计</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">直接费+措施费+间接费+利润+税金</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
-      </c>
-      <c r="E19">
-        <v>86458.680000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">编制人：自检</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">审核人：</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">日期：2026-10-24</t>
+          <t xml:space="preserve">审核人：—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日期：2026-10-30</t>
         </is>
       </c>
     </row>
@@ -457,6 +342,591 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="7.2" customWidth="1"/>
+    <col min="2" max="2" width="26.4" customWidth="1"/>
+    <col min="3" max="3" width="31.2" customWidth="1"/>
+    <col min="4" max="4" width="10.8" customWidth="1"/>
+    <col min="5" max="5" width="16.8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑安装工程费用预算表（表二）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">序号</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">费用名称</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">计算基数</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">费率</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金额（元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">直接费</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>403468.670000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">技工 731.80 工日 + 普工 1848.78 工日</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>196200.780000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主要材料费</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>42440.890000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助材料费</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 × 0.300%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.300%</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>588.600000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械使用费</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">详见表三乙</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>7912</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仪表使用费</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">详见表三丙</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>156326.400000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">直接费小计</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1+2+3+4+5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>403468.670000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">二</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">措施费</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>9810.040000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">安全文明施工费</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.500%</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>4905.020000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">临时设施费</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.500%</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>2943.010000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">冬雨季施工增加费</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.000%</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>1962.010000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规费</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>49050.200000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">社会保障费</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16.000%</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>31392.120000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住房公积金</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8.000%</t>
+        </is>
+      </c>
+      <c r="E18">
+        <v>15696.060000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工伤保险费</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.000%</t>
+        </is>
+      </c>
+      <c r="E19">
+        <v>1962.010000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">四</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">企业管理费</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E20">
+        <v>37278.150000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">企业管理费</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000%</t>
+        </is>
+      </c>
+      <c r="E21">
+        <v>35316.140000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">财务费用</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.000%</t>
+        </is>
+      </c>
+      <c r="E22">
+        <v>1962.010000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">利润</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E23">
+        <v>13734.050000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">利润</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工费 196,200.78</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.000%</t>
+        </is>
+      </c>
+      <c r="E24">
+        <v>13734.050000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">六</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">税金</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>46200.700000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">税金（增值税）</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">直接费+措施费+间接费+利润 513,341.11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.000%</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>46200.700000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑安装工程费合计</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">直接费+措施费+间接费+利润+税金</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E27">
+        <v>559541.800000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑安装工程费（大写）</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伍拾伍万玖仟伍佰肆拾壹元捌角整</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">编制人：示例</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">审核人：—</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日期：2026-10-30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="6.0" customWidth="1"/>
@@ -478,14 +948,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">定额明细表（表二）</t>
+          <t xml:space="preserve">建筑安装工程量预算表（表三甲）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">工程编号：ZT-2026-001　工程名称：自检工程-架空光缆　专业：有线通信　建设单位：某运营商　施工单位：某工程公司</t>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
         </is>
       </c>
     </row>
@@ -582,19 +1052,19 @@
         </is>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>6.720000</v>
+        <v>67.200000</v>
       </c>
       <c r="H5">
-        <v>1.680000</v>
+        <v>16.800000</v>
       </c>
       <c r="I5">
-        <v>868.560000</v>
+        <v>8685.600000</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -603,15 +1073,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2592</v>
       </c>
       <c r="M5">
-        <v>871.170000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">施工测量 12 百米</t>
-        </is>
+        <v>11303.660000</v>
       </c>
     </row>
     <row r="6">
@@ -620,38 +1085,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TXL2-001</t>
+          <t xml:space="preserve">TXL3-101</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">挖、松填光（电）缆沟及接头坑 普通土</t>
+          <t xml:space="preserve">木杆卡固法装 7/2.6 单股拉线 坚石</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">百立方米</t>
+          <t xml:space="preserve">条</t>
         </is>
       </c>
       <c r="E6">
-        <v>8.500000</v>
+        <v>60</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
-        </is>
+      <c r="G6">
+        <v>109.200000</v>
       </c>
       <c r="H6">
-        <v>334.730000</v>
+        <v>4.200000</v>
       </c>
       <c r="I6">
-        <v>20418.530000</v>
+        <v>12705</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>27465.900000</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -660,12 +1123,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>20479.790000</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">挖填缆沟</t>
-        </is>
+        <v>40209.020000</v>
       </c>
     </row>
     <row r="7">
@@ -688,19 +1146,19 @@
         </is>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>2.100000</v>
+        <v>4.200000</v>
       </c>
       <c r="H7">
-        <v>0.540000</v>
+        <v>1.080000</v>
       </c>
       <c r="I7">
-        <v>272.340000</v>
+        <v>544.680000</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -709,15 +1167,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>115.200000</v>
       </c>
       <c r="M7">
-        <v>273.160000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">施工测量（管道）</t>
-        </is>
+        <v>661.510000</v>
       </c>
     </row>
     <row r="8">
@@ -726,33 +1179,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TXL1-001</t>
+          <t xml:space="preserve">TXL2-001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">光（电）缆工程施工测量 直埋</t>
+          <t xml:space="preserve">挖、松填光（电）缆沟及接头坑 普通土</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">百米</t>
+          <t xml:space="preserve">百立方米</t>
         </is>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>2.800000</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="H8">
-        <v>0.700000</v>
+        <v>1772.100000</v>
       </c>
       <c r="I8">
-        <v>361.900000</v>
+        <v>108098.100000</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -764,12 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>362.990000</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">重复行</t>
-        </is>
+        <v>108422.390000</v>
       </c>
     </row>
     <row r="9">
@@ -778,33 +1228,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TXL3-222</t>
+          <t xml:space="preserve">TXL1-005</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">架空自承式电缆 100 对以上</t>
+          <t xml:space="preserve">GPS 定位</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">千米条</t>
+          <t xml:space="preserve">点</t>
         </is>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>174.800000</v>
-      </c>
-      <c r="H9">
-        <v>182</v>
+        <v>0.400000</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
       </c>
       <c r="I9">
-        <v>31029.200000</v>
+        <v>45.600000</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -813,29 +1265,48 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>19.200000</v>
       </c>
       <c r="M9">
-        <v>31122.290000</v>
+        <v>64.940000</v>
       </c>
     </row>
     <row r="10">
+      <c r="A10">
+        <v>6</v>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">合计</t>
-        </is>
+          <t xml:space="preserve">TXL3-102</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">木杆卡固法装 7/3.0 单股拉线 综合土</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">条</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>186.420000</v>
+        <v>26.400000</v>
       </c>
       <c r="H10">
-        <v>519.650000</v>
+        <v>18</v>
       </c>
       <c r="I10">
-        <v>52950.530000</v>
+        <v>4107.600000</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>14319.790000</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -844,17 +1315,753 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>53109.380000</v>
+        <v>18439.710000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSW5-206</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔深 30m 以下</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">m³</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>24.400000</v>
+      </c>
+      <c r="H11">
+        <v>36.600000</v>
+      </c>
+      <c r="I11">
+        <v>5014.200000</v>
+      </c>
+      <c r="J11">
+        <v>655.200000</v>
+      </c>
+      <c r="K11">
+        <v>7912</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>13596.440000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSW4-116</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中心站站内环测</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">站</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>500</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>57000</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>153600</v>
+      </c>
+      <c r="M12">
+        <v>210771</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合计</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>731.800000</v>
+      </c>
+      <c r="H13">
+        <v>1848.780000</v>
+      </c>
+      <c r="I13">
+        <v>196200.780000</v>
+      </c>
+      <c r="J13">
+        <v>42440.890000</v>
+      </c>
+      <c r="K13">
+        <v>7912</v>
+      </c>
+      <c r="L13">
+        <v>156326.400000</v>
+      </c>
+      <c r="M13">
+        <v>403468.670000</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="6.0" customWidth="1"/>
+    <col min="1" max="1" width="7.2" customWidth="1"/>
+    <col min="2" max="2" width="36.0" customWidth="1"/>
+    <col min="3" max="3" width="31.2" customWidth="1"/>
+    <col min="4" max="4" width="9.6" customWidth="1"/>
+    <col min="5" max="5" width="12.0" customWidth="1"/>
+    <col min="6" max="6" width="14.4" customWidth="1"/>
+    <col min="7" max="7" width="16.8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑安装工程机械使用费预算表（表三乙）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">序号</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">名称</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规格程式</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单位</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班数</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价（元）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金额（元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机动绞磨</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>2.800000</v>
+      </c>
+      <c r="F5">
+        <v>860</v>
+      </c>
+      <c r="G5">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">污水泵</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>0.800000</v>
+      </c>
+      <c r="F6">
+        <v>860</v>
+      </c>
+      <c r="G6">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">混凝土振捣机</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>0.800000</v>
+      </c>
+      <c r="F7">
+        <v>860</v>
+      </c>
+      <c r="G7">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">混凝土搅拌机</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>0.800000</v>
+      </c>
+      <c r="F8">
+        <v>860</v>
+      </c>
+      <c r="G8">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电动卷扬机 3t</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>3.200000</v>
+      </c>
+      <c r="F9">
+        <v>860</v>
+      </c>
+      <c r="G9">
+        <v>2752</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">载重汽车 5t</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>0.800000</v>
+      </c>
+      <c r="F10">
+        <v>860</v>
+      </c>
+      <c r="G10">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合计</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>7912</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="7.2" customWidth="1"/>
+    <col min="2" max="2" width="36.0" customWidth="1"/>
+    <col min="3" max="3" width="31.2" customWidth="1"/>
+    <col min="4" max="4" width="9.6" customWidth="1"/>
+    <col min="5" max="5" width="12.0" customWidth="1"/>
+    <col min="6" max="6" width="14.4" customWidth="1"/>
+    <col min="7" max="7" width="16.8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑安装工程仪器仪表使用费预算表（表三丙）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">序号</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">名称</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规格程式</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单位</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班数</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">单价（元）</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金额（元）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GPS 定位仪</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>0.080000</v>
+      </c>
+      <c r="F5">
+        <v>240</v>
+      </c>
+      <c r="G5">
+        <v>19.200000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中频噪声发生器</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>240</v>
+      </c>
+      <c r="G6">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">信令分析仪</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="F7">
+        <v>240</v>
+      </c>
+      <c r="G7">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">协议分析仪</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <v>240</v>
+      </c>
+      <c r="G8">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地下管线探测仪</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>240</v>
+      </c>
+      <c r="G9">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射频功率计</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <v>240</v>
+      </c>
+      <c r="G10">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">微波线路分析仪</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <v>240</v>
+      </c>
+      <c r="G11">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">微波网络分析仪</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
+        <v>240</v>
+      </c>
+      <c r="G12">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">微波频率计</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <v>240</v>
+      </c>
+      <c r="G13">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">测试变频器</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E14">
+        <v>40</v>
+      </c>
+      <c r="F14">
+        <v>240</v>
+      </c>
+      <c r="G14">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">激光测距仪</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E15">
+        <v>5.280000</v>
+      </c>
+      <c r="F15">
+        <v>240</v>
+      </c>
+      <c r="G15">
+        <v>1267.200000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">误码测试仪</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E16">
+        <v>80</v>
+      </c>
+      <c r="F16">
+        <v>240</v>
+      </c>
+      <c r="G16">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">频谱分析仪</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台班</t>
+        </is>
+      </c>
+      <c r="E17">
+        <v>120</v>
+      </c>
+      <c r="F17">
+        <v>240</v>
+      </c>
+      <c r="G17">
+        <v>28800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合计</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>156326.400000</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="8.4" customWidth="1"/>
     <col min="2" max="2" width="9.6" customWidth="1"/>
     <col min="3" max="3" width="31.2" customWidth="1"/>
     <col min="4" max="4" width="26.4" customWidth="1"/>
@@ -867,14 +2074,14 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">主要材料（设备）表</t>
+          <t xml:space="preserve">器材预算表（表四甲 · 国内器材）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">工程编号：ZT-2026-001　工程名称：自检工程-架空光缆　专业：有线通信　建设单位：某运营商　施工单位：某工程公司</t>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
         </is>
       </c>
     </row>
@@ -887,7 +2094,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
+          <t xml:space="preserve">类别</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -932,22 +2139,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">L 型挂钩</t>
+          <t xml:space="preserve">地锚铁柄</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">只</t>
+          <t xml:space="preserve">套</t>
         </is>
       </c>
       <c r="F5">
-        <v>252.500000</v>
+        <v>30.300000</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>848.400000</v>
       </c>
     </row>
     <row r="6">
@@ -961,22 +2168,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">U 型卡子②</t>
+          <t xml:space="preserve">岩石钢地锚</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">个</t>
+          <t xml:space="preserve">套</t>
         </is>
       </c>
       <c r="F6">
-        <v>272.700000</v>
+        <v>60.600000</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1696.800000</v>
       </c>
     </row>
     <row r="7">
@@ -990,22 +2197,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">三眼双曲槽夹板</t>
+          <t xml:space="preserve">扒钉</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">副</t>
+          <t xml:space="preserve">kg</t>
         </is>
       </c>
       <c r="F7">
-        <v>20.200000</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -1019,22 +2226,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">单眼曲槽夹板</t>
+          <t xml:space="preserve">拉线衬环</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">副</t>
+          <t xml:space="preserve">个</t>
         </is>
       </c>
       <c r="F8">
-        <v>292.900000</v>
+        <v>90.900000</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2545.200000</v>
       </c>
     </row>
     <row r="9">
@@ -1048,22 +2255,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">吊线抱箍</t>
+          <t xml:space="preserve">木模板</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">套</t>
+          <t xml:space="preserve">m³</t>
         </is>
       </c>
       <c r="F9">
-        <v>282.800000</v>
+        <v>0.400000</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>11.200000</v>
       </c>
     </row>
     <row r="10">
@@ -1077,22 +2284,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">吊线担</t>
+          <t xml:space="preserve">条形护杆板</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">根</t>
+          <t xml:space="preserve">块</t>
         </is>
       </c>
       <c r="F10">
-        <v>282.800000</v>
+        <v>363.600000</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>10180.800000</v>
       </c>
     </row>
     <row r="11">
@@ -1106,22 +2313,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">圆帽穿钉 M12×60</t>
+          <t xml:space="preserve">水泥拉线盘</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">副</t>
+          <t xml:space="preserve">套</t>
         </is>
       </c>
       <c r="F11">
-        <v>252.500000</v>
+        <v>30.300000</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.620000</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>18.790000</v>
       </c>
     </row>
     <row r="12">
@@ -1135,22 +2342,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">圆帽穿钉 M12×80</t>
+          <t xml:space="preserve">混凝土</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">副</t>
+          <t xml:space="preserve">m³</t>
         </is>
       </c>
       <c r="F12">
-        <v>252.500000</v>
+        <v>20.400000</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>571.200000</v>
       </c>
     </row>
     <row r="13">
@@ -1164,22 +2371,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">多用二线钢担</t>
+          <t xml:space="preserve">瓦形护杆板</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">根</t>
+          <t xml:space="preserve">块</t>
         </is>
       </c>
       <c r="F13">
-        <v>282.800000</v>
+        <v>181.800000</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>5090.400000</v>
       </c>
     </row>
     <row r="14">
@@ -1193,22 +2400,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">小拉板</t>
+          <t xml:space="preserve">钢线卡子</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">块</t>
+          <t xml:space="preserve">个</t>
         </is>
       </c>
       <c r="F14">
-        <v>30.300000</v>
+        <v>545.400000</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>15271.200000</v>
       </c>
     </row>
     <row r="15">
@@ -1222,22 +2429,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">拉线抱箍</t>
+          <t xml:space="preserve">镀锌钢绞线</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">套</t>
+          <t xml:space="preserve">kg</t>
         </is>
       </c>
       <c r="F15">
-        <v>40.400000</v>
+        <v>441</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>12.500000</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>5512.500000</v>
       </c>
     </row>
     <row r="16">
@@ -1251,22 +2458,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">拉线衬环</t>
+          <t xml:space="preserve">镀锌铁丝 综合</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">个</t>
+          <t xml:space="preserve">kg</t>
         </is>
       </c>
       <c r="F16">
-        <v>90.900000</v>
+        <v>1.600000</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>44.800000</v>
       </c>
     </row>
     <row r="17">
@@ -1280,22 +2487,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">终端可变抱箍</t>
+          <t xml:space="preserve">镀锌铁线 ø1.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">套</t>
+          <t xml:space="preserve">kg</t>
         </is>
       </c>
       <c r="F17">
-        <v>60.600000</v>
+        <v>2.400000</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>67.200000</v>
       </c>
     </row>
     <row r="18">
@@ -1309,294 +2516,59 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">自承式电缆</t>
+          <t xml:space="preserve">镀锌铁线 ø4.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">m</t>
+          <t xml:space="preserve">kg</t>
         </is>
       </c>
       <c r="F18">
-        <v>10070</v>
+        <v>19.800000</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>554.400000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>15</v>
-      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">转弯夹板</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">副</t>
-        </is>
-      </c>
-      <c r="F19">
-        <v>20.200000</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
+          <t xml:space="preserve">合计</t>
+        </is>
       </c>
       <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>16</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">钢担 U 型抱箍（二线担用）</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">套</t>
-        </is>
-      </c>
-      <c r="F20">
-        <v>282.800000</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>17</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">钢线双向膨胀锁</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">只</t>
-        </is>
-      </c>
-      <c r="F21">
-        <v>20.200000</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">钢线终端膨胀锁</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">只</t>
-        </is>
-      </c>
-      <c r="F22">
-        <v>90.900000</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>19</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">镀锌穿钉 M12×80</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">副</t>
-        </is>
-      </c>
-      <c r="F23">
-        <v>10.100000</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>20</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">镀锌钢绞线 7/2.2</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F24">
-        <v>25</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">镀锌铁线 ø1.5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F25">
-        <v>7.100000</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>22</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">主材</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">镀锌铁线 ø2.0</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kg</t>
-        </is>
-      </c>
-      <c r="F26">
-        <v>10.200000</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">合计</t>
-        </is>
-      </c>
-      <c r="H27">
-        <v>0</v>
+        <v>42440.890000</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="6.0" customWidth="1"/>
-    <col min="2" max="2" width="9.6" customWidth="1"/>
+    <col min="1" max="1" width="7.2" customWidth="1"/>
+    <col min="2" max="2" width="26.4" customWidth="1"/>
     <col min="3" max="3" width="31.2" customWidth="1"/>
-    <col min="4" max="4" width="26.4" customWidth="1"/>
-    <col min="5" max="5" width="8.4" customWidth="1"/>
-    <col min="6" max="6" width="12.0" customWidth="1"/>
-    <col min="7" max="7" width="14.4" customWidth="1"/>
-    <col min="8" max="8" width="16.8" customWidth="1"/>
+    <col min="4" max="4" width="10.8" customWidth="1"/>
+    <col min="5" max="5" width="16.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">机械仪表台班表</t>
+          <t xml:space="preserve">工程建设其他费预算表（表五甲）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">工程编号：ZT-2026-001　工程名称：自检工程-架空光缆　专业：有线通信　建设单位：某运营商　施工单位：某工程公司</t>
+          <t xml:space="preserve">工程编号：DEMO-2026-001　工程名称：示例工程 · 架空光缆线路　专业：有线通信　建设单位：示例建设单位　施工单位：示例施工单位</t>
         </is>
       </c>
     </row>
@@ -1609,35 +2581,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型</t>
+          <t xml:space="preserve">费用名称</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">名称</t>
+          <t xml:space="preserve">计算基数</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">规格程式</t>
+          <t xml:space="preserve">费率</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单位</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台班数</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">单价（元）</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">金额（元）</t>
         </is>
@@ -1649,27 +2606,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">仪表</t>
+          <t xml:space="preserve">建设单位管理费</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">地下管线探测仪</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台班</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>0.850000</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+          <t xml:space="preserve">建筑安装工程费 559,541.80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.500%</t>
+        </is>
+      </c>
+      <c r="E5">
+        <v>8393.130000</v>
       </c>
     </row>
     <row r="6">
@@ -1678,37 +2629,114 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">仪表</t>
+          <t xml:space="preserve">勘察设计费</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">激光测距仪</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">台班</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>0.920000</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+          <t xml:space="preserve">建筑安装工程费 559,541.80</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.000%</t>
+        </is>
+      </c>
+      <c r="E6">
+        <v>16786.250000</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">合计</t>
-        </is>
-      </c>
-      <c r="H7">
-        <v>0</v>
+          <t xml:space="preserve">工程监理费</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建筑安装工程费 559,541.80</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.000%</t>
+        </is>
+      </c>
+      <c r="E7">
+        <v>11190.840000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工程建设其他费合计</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E8">
+        <v>36370.220000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基本预备费</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">建安工程费+设备费+其他费 595,912.02</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.000%</t>
+        </is>
+      </c>
+      <c r="E9">
+        <v>17877.360000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">预备费合计</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="E10">
+        <v>17877.360000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">编制人：示例</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">审核人：—</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日期：2026-10-30</t>
+        </is>
       </c>
     </row>
   </sheetData>
